--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -663,7 +663,7 @@
   </si>
   <si>
     <t>Coding of the severity with a terminology is preferred, where possible.  
-可能な限り、ターミノロジを用いて重症度をコーディングすることが好ましい。  
+可能な限り、ターミノロジを用いて重症度をコード化することが好ましい。  
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
